--- a/portfolio_data.xlsx
+++ b/portfolio_data.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marc\Programming\Python\stock-viz\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marc\Programming\Python\portfolio_overview\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A78C139C-4CD1-44D0-8B64-008856D67B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{942259D7-3BB4-44A3-AC60-2C60CB615C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52755" yWindow="1245" windowWidth="32880" windowHeight="18615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11655" yWindow="1515" windowWidth="35610" windowHeight="18615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="110">
   <si>
     <t>Midler</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Security</t>
   </si>
   <si>
+    <t>Mapped_Security</t>
+  </si>
+  <si>
     <t>Sektor</t>
   </si>
   <si>
@@ -79,271 +82,274 @@
     <t>Frie midler</t>
   </si>
   <si>
+    <t>Saxo</t>
+  </si>
+  <si>
+    <t>Saxo - Marc</t>
+  </si>
+  <si>
+    <t>Alibaba Group Holding Ltd</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
+    <t>Aktie</t>
+  </si>
+  <si>
+    <t>HKG:9988</t>
+  </si>
+  <si>
+    <t>9988.HK</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
+  <si>
+    <t>Saxo - Amina</t>
+  </si>
+  <si>
+    <t>BP plc</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>LON:BP</t>
+  </si>
+  <si>
+    <t>BP.L</t>
+  </si>
+  <si>
+    <t>GBp</t>
+  </si>
+  <si>
+    <t>DS NORDEN A/S</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>DNORD</t>
+  </si>
+  <si>
+    <t>DNORD.CO</t>
+  </si>
+  <si>
+    <t>DKK</t>
+  </si>
+  <si>
+    <t>Nordnet</t>
+  </si>
+  <si>
+    <t>Nordnet - Amina - Depot - Fonde</t>
+  </si>
+  <si>
+    <t>Danske Inv Global Indeks, kl DKK d</t>
+  </si>
+  <si>
+    <t>Global Index Fund</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>ETF</t>
+  </si>
+  <si>
+    <t>DKIGI</t>
+  </si>
+  <si>
+    <t>DKIGI.CO</t>
+  </si>
+  <si>
+    <t>Marc - Depot - Fonde</t>
+  </si>
+  <si>
+    <t>Dsv A/S</t>
+  </si>
+  <si>
+    <t>CPH:DSV</t>
+  </si>
+  <si>
+    <t>DSV.CO</t>
+  </si>
+  <si>
+    <t>FLSmidth &amp; Co A/S</t>
+  </si>
+  <si>
+    <t>CPH:FLS</t>
+  </si>
+  <si>
+    <t>FLS.CO</t>
+  </si>
+  <si>
+    <t>NKT A/S</t>
+  </si>
+  <si>
+    <t>CPH:NKT</t>
+  </si>
+  <si>
+    <t>NKT.CO</t>
+  </si>
+  <si>
+    <t>Novo Nordisk B A/S</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>CPH:NOVO-B</t>
+  </si>
+  <si>
+    <t>NOVO-B.CO</t>
+  </si>
+  <si>
+    <t>Nordnet - Amina - Aktiedepot</t>
+  </si>
+  <si>
+    <t>Sea Ltd</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>Storebrand Indeks - Alle Markeder A5</t>
+  </si>
+  <si>
+    <t>STIIAM.ST</t>
+  </si>
+  <si>
+    <t>Walt Disney Co</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>DIS</t>
+  </si>
+  <si>
+    <t>XACT OMXC25 ESG (UCITS ETF)</t>
+  </si>
+  <si>
+    <t>OMXC25 Fund</t>
+  </si>
+  <si>
+    <t>CPH:XACTC25</t>
+  </si>
+  <si>
+    <t>XACTC25.CO</t>
+  </si>
+  <si>
+    <t>Xtrackers Euro Stoxx 50 UCITS ETF 1C</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Euro Stoxx 50</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>BIT:XESC</t>
+  </si>
+  <si>
+    <t>XESC.DE</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>Marc - Depot - ETFer</t>
+  </si>
+  <si>
+    <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
+  </si>
+  <si>
+    <t>Emerging Markets Fund</t>
+  </si>
+  <si>
+    <t>BIT:XMME</t>
+  </si>
+  <si>
+    <t>XMME.DE</t>
+  </si>
+  <si>
     <t>Pension</t>
   </si>
   <si>
-    <t>Saxo</t>
-  </si>
-  <si>
-    <t>Nordnet</t>
-  </si>
-  <si>
-    <t>Saxo - Marc</t>
-  </si>
-  <si>
-    <t>Saxo - Amina</t>
-  </si>
-  <si>
-    <t>Nordnet - Amina - Depot - Fonde</t>
-  </si>
-  <si>
-    <t>Marc - Depot - Fonde</t>
-  </si>
-  <si>
-    <t>Nordnet - Amina - Aktiedepot</t>
-  </si>
-  <si>
-    <t>Marc - Depot - ETFer</t>
+    <t>Xtrackers MSCI World Materials UCITS ETF 1C</t>
+  </si>
+  <si>
+    <t>Materials Fund</t>
+  </si>
+  <si>
+    <t>BIT:XDWM</t>
+  </si>
+  <si>
+    <t>XDWM.DE</t>
+  </si>
+  <si>
+    <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
+  </si>
+  <si>
+    <t>S&amp;P 500 Fund</t>
+  </si>
+  <si>
+    <t>BIT:CSSPX</t>
+  </si>
+  <si>
+    <t>CSSPX.MI</t>
   </si>
   <si>
     <t>Nordnet - Amina - Ratepension</t>
   </si>
   <si>
+    <t>iShares Digital Security UCITS ETF USD (Acc)</t>
+  </si>
+  <si>
+    <t>Digital Security Fund</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>LOCK</t>
+  </si>
+  <si>
+    <t>LOCK.L</t>
+  </si>
+  <si>
     <t>Nordnet - Amina - Aldersopsparing</t>
   </si>
   <si>
+    <t>iShares MSCI ACWI USD Acc UCITS ETF</t>
+  </si>
+  <si>
+    <t>IUSQ</t>
+  </si>
+  <si>
+    <t>IUSQ.DE</t>
+  </si>
+  <si>
     <t>Marc - Aldersopsparing</t>
   </si>
   <si>
-    <t>Alibaba Group Holding Ltd</t>
-  </si>
-  <si>
-    <t>BP plc</t>
-  </si>
-  <si>
-    <t>DS NORDEN A/S</t>
-  </si>
-  <si>
-    <t>Danske Inv Global Indeks, kl DKK d</t>
-  </si>
-  <si>
-    <t>Dsv A/S</t>
-  </si>
-  <si>
-    <t>FLSmidth &amp; Co A/S</t>
-  </si>
-  <si>
-    <t>NKT A/S</t>
-  </si>
-  <si>
-    <t>Novo Nordisk B A/S</t>
-  </si>
-  <si>
-    <t>Sea Ltd</t>
-  </si>
-  <si>
-    <t>Storebrand Indeks - Alle Markeder A5</t>
-  </si>
-  <si>
-    <t>Walt Disney Co</t>
-  </si>
-  <si>
-    <t>XACT OMXC25 ESG (UCITS ETF)</t>
-  </si>
-  <si>
-    <t>Xtrackers Euro Stoxx 50 UCITS ETF 1C</t>
-  </si>
-  <si>
-    <t>Xtrackers MSCI Emerging Markets UCITS ETF 1C</t>
-  </si>
-  <si>
-    <t>Xtrackers MSCI World Materials UCITS ETF 1C</t>
-  </si>
-  <si>
-    <t>iShares Core S&amp;P 500 UCITS ETF USD (Acc)</t>
-  </si>
-  <si>
-    <t>iShares Digital Security UCITS ETF USD (Acc)</t>
-  </si>
-  <si>
-    <t>iShares MSCI ACWI USD Acc UCITS ETF</t>
-  </si>
-  <si>
     <t>iShares S&amp;P 500 Info Technolg Sctr UCITS ETF USD A</t>
   </si>
   <si>
-    <t>Consumer Cyclical</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>Communication Services</t>
-  </si>
-  <si>
-    <t>Aktie</t>
-  </si>
-  <si>
-    <t>ETF</t>
-  </si>
-  <si>
-    <t>HKG:9988</t>
-  </si>
-  <si>
-    <t>LON:BP</t>
-  </si>
-  <si>
-    <t>DNORD</t>
-  </si>
-  <si>
-    <t>DKIGI</t>
-  </si>
-  <si>
-    <t>CPH:DSV</t>
-  </si>
-  <si>
-    <t>CPH:FLS</t>
-  </si>
-  <si>
-    <t>CPH:NKT</t>
-  </si>
-  <si>
-    <t>CPH:NOVO-B</t>
-  </si>
-  <si>
-    <t>NOVO-B.CO</t>
-  </si>
-  <si>
-    <t>SE</t>
-  </si>
-  <si>
-    <t>DIS</t>
-  </si>
-  <si>
-    <t>CPH:XACTC25</t>
-  </si>
-  <si>
-    <t>BIT:XESC</t>
-  </si>
-  <si>
-    <t>BIT:XMME</t>
-  </si>
-  <si>
-    <t>BIT:XDWM</t>
-  </si>
-  <si>
-    <t>BIT:CSSPX</t>
-  </si>
-  <si>
-    <t>LOCK</t>
-  </si>
-  <si>
-    <t>IUSQ</t>
+    <t>S&amp;P 500 IT Fund</t>
   </si>
   <si>
     <t>OTCMKTS:ISRCF</t>
   </si>
   <si>
-    <t>9988.HK</t>
-  </si>
-  <si>
-    <t>BP.L</t>
-  </si>
-  <si>
-    <t>DNORD.CO</t>
-  </si>
-  <si>
-    <t>DKIGI.CO</t>
-  </si>
-  <si>
-    <t>DSV.CO</t>
-  </si>
-  <si>
-    <t>FLS.CO</t>
-  </si>
-  <si>
-    <t>NKT.CO</t>
-  </si>
-  <si>
-    <t>STIIAM.ST</t>
-  </si>
-  <si>
-    <t>XACTC25.CO</t>
-  </si>
-  <si>
-    <t>XESC.DE</t>
-  </si>
-  <si>
-    <t>XMME.DE</t>
-  </si>
-  <si>
-    <t>XDWM.DE</t>
-  </si>
-  <si>
-    <t>CSSPX.MI</t>
-  </si>
-  <si>
-    <t>LOCK.L</t>
-  </si>
-  <si>
-    <t>IUSQ.DE</t>
-  </si>
-  <si>
     <t>QDVE.DE</t>
-  </si>
-  <si>
-    <t>US</t>
-  </si>
-  <si>
-    <t>HKD</t>
-  </si>
-  <si>
-    <t>GBp</t>
-  </si>
-  <si>
-    <t>DKK</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>EUR</t>
-  </si>
-  <si>
-    <t>Mapped_Security</t>
-  </si>
-  <si>
-    <t>Global Index Fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Euro Stoxx 50</t>
-  </si>
-  <si>
-    <t>Emerging Markets Fund</t>
-  </si>
-  <si>
-    <t>S&amp;P 500 Fund</t>
-  </si>
-  <si>
-    <t>Digital Security Fund</t>
-  </si>
-  <si>
-    <t>S&amp;P 500 IT Fund</t>
-  </si>
-  <si>
-    <t>Materials Fund</t>
-  </si>
-  <si>
-    <t>OMXC25 Fund</t>
   </si>
 </sst>
 </file>
@@ -361,24 +367,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3D3D3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -410,7 +407,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -429,9 +428,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -469,7 +468,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -503,7 +502,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -538,10 +536,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -718,22 +715,8 @@
   <dimension ref="A1:S40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" customWidth="1"/>
-    <col min="3" max="3" width="33.7109375" customWidth="1"/>
-    <col min="4" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" customWidth="1"/>
-    <col min="8" max="9" width="13.7109375" customWidth="1"/>
-    <col min="10" max="10" width="6.7109375" customWidth="1"/>
-    <col min="11" max="11" width="5.7109375" customWidth="1"/>
-    <col min="12" max="12" width="7.7109375" customWidth="1"/>
-    <col min="13" max="13" width="8.7109375" customWidth="1"/>
-    <col min="14" max="15" width="18.7109375" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" customWidth="1"/>
-    <col min="18" max="18" width="6.7109375" customWidth="1"/>
-    <col min="19" max="19" width="17.7109375" customWidth="1"/>
+    <col min="4" max="4" width="46.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -750,81 +733,81 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
-        <v>31</v>
-      </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K2">
         <v>400</v>
@@ -833,22 +816,22 @@
         <v>93.78</v>
       </c>
       <c r="M2" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="N2">
         <v>116.3000030517578</v>
       </c>
       <c r="O2">
-        <v>37948.691128883373</v>
+        <v>46520.001220703118</v>
       </c>
       <c r="P2">
-        <v>-4200.49</v>
+        <v>-5642.8761480712892</v>
       </c>
       <c r="Q2">
         <v>-12.13</v>
       </c>
       <c r="R2">
-        <v>2.8</v>
+        <v>6.9497163157285806</v>
       </c>
       <c r="S2">
         <v>0.81575000286102295</v>
@@ -856,34 +839,34 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" t="s">
-        <v>50</v>
-      </c>
       <c r="G3" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K3">
         <v>100</v>
@@ -892,22 +875,22 @@
         <v>165</v>
       </c>
       <c r="M3" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="N3">
         <v>116.3000030517578</v>
       </c>
       <c r="O3">
-        <v>9487.1727822208413</v>
+        <v>34890.000915527336</v>
       </c>
       <c r="P3">
-        <v>-7625.51</v>
+        <v>-17465.93445831299</v>
       </c>
       <c r="Q3">
         <v>-50.06</v>
       </c>
       <c r="R3">
-        <v>0.7</v>
+        <v>5.2122872367964357</v>
       </c>
       <c r="S3">
         <v>0.81575000286102295</v>
@@ -915,34 +898,34 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
         <v>32</v>
       </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G4" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" t="s">
-        <v>59</v>
-      </c>
       <c r="I4" t="s">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="J4" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K4">
         <v>6.18</v>
@@ -951,22 +934,22 @@
         <v>3</v>
       </c>
       <c r="M4" t="s">
-        <v>95</v>
+        <v>34</v>
       </c>
       <c r="N4">
         <v>423.20001220703119</v>
       </c>
       <c r="O4">
-        <v>22532.90345450255</v>
+        <v>2615.376075439453</v>
       </c>
       <c r="P4">
-        <v>5191.21</v>
+        <v>815.21272271447742</v>
       </c>
       <c r="Q4">
         <v>31.17</v>
       </c>
       <c r="R4">
-        <v>1.7</v>
+        <v>0.3907162791551842</v>
       </c>
       <c r="S4">
         <v>8.6155500411987305</v>
@@ -974,34 +957,34 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G5" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="I5" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="J5" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K5">
         <v>90</v>
@@ -1010,7 +993,7 @@
         <v>162.5</v>
       </c>
       <c r="M5" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="N5">
         <v>241.80000305175781</v>
@@ -1019,13 +1002,13 @@
         <v>21762.000274658199</v>
       </c>
       <c r="P5">
-        <v>4491</v>
+        <v>6683.1102843475346</v>
       </c>
       <c r="Q5">
         <v>30.71</v>
       </c>
       <c r="R5">
-        <v>1.6</v>
+        <v>3.251068882267671</v>
       </c>
       <c r="S5">
         <v>1</v>
@@ -1033,34 +1016,34 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H6" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="I6" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="J6" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K6">
         <v>89</v>
@@ -1069,7 +1052,7 @@
         <v>164.8</v>
       </c>
       <c r="M6" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="N6">
         <v>157.6499938964844</v>
@@ -1078,13 +1061,13 @@
         <v>14030.849456787109</v>
       </c>
       <c r="P6">
-        <v>4.62</v>
+        <v>74.363502120971688</v>
       </c>
       <c r="Q6">
         <v>0.53</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <v>2.096096750529945</v>
       </c>
       <c r="S6">
         <v>1</v>
@@ -1092,34 +1075,34 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="I7" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="J7" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K7">
         <v>602</v>
@@ -1128,22 +1111,22 @@
         <v>148.46</v>
       </c>
       <c r="M7" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="N7">
         <v>157.6499938964844</v>
       </c>
       <c r="O7">
-        <v>94905.296325683594</v>
+        <v>94905.296325683608</v>
       </c>
       <c r="P7">
-        <v>4.62</v>
+        <v>502.99807052612312</v>
       </c>
       <c r="Q7">
         <v>0.53</v>
       </c>
       <c r="R7">
-        <v>7.1</v>
+        <v>14.17809262718008</v>
       </c>
       <c r="S7">
         <v>1</v>
@@ -1151,34 +1134,34 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="H8" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="I8" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="J8" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K8">
         <v>12</v>
@@ -1187,7 +1170,7 @@
         <v>976.4</v>
       </c>
       <c r="M8" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="N8">
         <v>1487</v>
@@ -1196,13 +1179,13 @@
         <v>17844</v>
       </c>
       <c r="P8">
-        <v>6631.2</v>
+        <v>10099.704</v>
       </c>
       <c r="Q8">
         <v>56.6</v>
       </c>
       <c r="R8">
-        <v>1.3</v>
+        <v>2.665750960528166</v>
       </c>
       <c r="S8">
         <v>1</v>
@@ -1210,34 +1193,34 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="H9" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="I9" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="J9" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K9">
         <v>9</v>
@@ -1246,7 +1229,7 @@
         <v>1512</v>
       </c>
       <c r="M9" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="N9">
         <v>1487</v>
@@ -1255,13 +1238,13 @@
         <v>13383</v>
       </c>
       <c r="P9">
-        <v>153</v>
+        <v>149.8896</v>
       </c>
       <c r="Q9">
         <v>1.1200000000000001</v>
       </c>
       <c r="R9">
-        <v>1</v>
+        <v>1.999313220396125</v>
       </c>
       <c r="S9">
         <v>1</v>
@@ -1269,34 +1252,34 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" t="s">
         <v>36</v>
       </c>
-      <c r="E10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" t="s">
-        <v>52</v>
-      </c>
       <c r="G10" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="H10" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="I10" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="J10" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K10">
         <v>91</v>
@@ -1305,7 +1288,7 @@
         <v>229.77</v>
       </c>
       <c r="M10" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="N10">
         <v>382.79998779296881</v>
@@ -1314,13 +1297,13 @@
         <v>34834.798889160164</v>
       </c>
       <c r="P10">
-        <v>11486.93</v>
+        <v>19138.238509704599</v>
       </c>
       <c r="Q10">
         <v>54.94</v>
       </c>
       <c r="R10">
-        <v>2.6</v>
+        <v>5.204040495325275</v>
       </c>
       <c r="S10">
         <v>1</v>
@@ -1328,34 +1311,34 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" t="s">
         <v>36</v>
       </c>
-      <c r="E11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" t="s">
-        <v>52</v>
-      </c>
       <c r="G11" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="H11" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="J11" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K11">
         <v>36</v>
@@ -1364,7 +1347,7 @@
         <v>272.10000000000002</v>
       </c>
       <c r="M11" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="N11">
         <v>382.79998779296881</v>
@@ -1373,13 +1356,13 @@
         <v>13780.79956054688</v>
       </c>
       <c r="P11">
-        <v>3020.4</v>
+        <v>4248.6205045166016</v>
       </c>
       <c r="Q11">
         <v>30.83</v>
       </c>
       <c r="R11">
-        <v>1</v>
+        <v>2.058741294853955</v>
       </c>
       <c r="S11">
         <v>1</v>
@@ -1387,34 +1370,34 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
         <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" t="s">
         <v>56</v>
       </c>
-      <c r="H12" t="s">
-        <v>64</v>
-      </c>
       <c r="I12" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="J12" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K12">
         <v>61</v>
@@ -1423,7 +1406,7 @@
         <v>305</v>
       </c>
       <c r="M12" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="N12">
         <v>557.5</v>
@@ -1432,13 +1415,13 @@
         <v>34007.5</v>
       </c>
       <c r="P12">
-        <v>12779.5</v>
+        <v>23359.751749999999</v>
       </c>
       <c r="Q12">
         <v>68.69</v>
       </c>
       <c r="R12">
-        <v>2.5</v>
+        <v>5.0804486544587322</v>
       </c>
       <c r="S12">
         <v>1</v>
@@ -1446,34 +1429,34 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" t="s">
         <v>56</v>
       </c>
-      <c r="H13" t="s">
-        <v>64</v>
-      </c>
       <c r="I13" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="J13" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K13">
         <v>66</v>
@@ -1482,7 +1465,7 @@
         <v>293.01</v>
       </c>
       <c r="M13" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="N13">
         <v>557.5</v>
@@ -1491,13 +1474,13 @@
         <v>36795</v>
       </c>
       <c r="P13">
-        <v>14618.34</v>
+        <v>27813.340499999998</v>
       </c>
       <c r="Q13">
         <v>75.59</v>
       </c>
       <c r="R13">
-        <v>2.7</v>
+        <v>5.4968788720373167</v>
       </c>
       <c r="S13">
         <v>1</v>
@@ -1505,34 +1488,34 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G14" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="H14" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="I14" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J14" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K14">
         <v>44</v>
@@ -1541,22 +1524,22 @@
         <v>440.25</v>
       </c>
       <c r="M14" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="N14">
         <v>323.04998779296881</v>
       </c>
       <c r="O14">
-        <v>14214.19946289062</v>
+        <v>14214.19946289063</v>
       </c>
       <c r="P14">
-        <v>8093.8</v>
+        <v>5938.6925355957037</v>
       </c>
       <c r="Q14">
         <v>41.78</v>
       </c>
       <c r="R14">
-        <v>1.1000000000000001</v>
+        <v>2.1234877757980071</v>
       </c>
       <c r="S14">
         <v>1</v>
@@ -1564,34 +1547,34 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F15" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G15" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="H15" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I15" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J15" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K15">
         <v>295</v>
@@ -1600,22 +1583,22 @@
         <v>430.79</v>
       </c>
       <c r="M15" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="N15">
         <v>323.04998779296881</v>
       </c>
       <c r="O15">
-        <v>95299.746398925781</v>
+        <v>95299.746398925796</v>
       </c>
       <c r="P15">
-        <v>2770.07</v>
+        <v>4726.8674213867189</v>
       </c>
       <c r="Q15">
         <v>4.96</v>
       </c>
       <c r="R15">
-        <v>7.1</v>
+        <v>14.237020315009371</v>
       </c>
       <c r="S15">
         <v>1</v>
@@ -1623,34 +1606,34 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
         <v>20</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F16" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G16" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="H16" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I16" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J16" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K16">
         <v>85</v>
@@ -1659,22 +1642,22 @@
         <v>579.77</v>
       </c>
       <c r="M16" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="N16">
         <v>323.04998779296881</v>
       </c>
       <c r="O16">
-        <v>27459.24896240234</v>
+        <v>27459.248962402351</v>
       </c>
       <c r="P16">
-        <v>2770.07</v>
+        <v>1361.978748535156</v>
       </c>
       <c r="Q16">
         <v>4.96</v>
       </c>
       <c r="R16">
-        <v>2</v>
+        <v>4.1021922941552411</v>
       </c>
       <c r="S16">
         <v>1</v>
@@ -1682,34 +1665,34 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E17" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F17" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G17" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="H17" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I17" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J17" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K17">
         <v>41</v>
@@ -1718,7 +1701,7 @@
         <v>602.71</v>
       </c>
       <c r="M17" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="N17">
         <v>323.04998779296881</v>
@@ -1727,13 +1710,13 @@
         <v>13245.049499511721</v>
       </c>
       <c r="P17">
-        <v>2770.07</v>
+        <v>656.95445517578128</v>
       </c>
       <c r="Q17">
         <v>4.96</v>
       </c>
       <c r="R17">
-        <v>1</v>
+        <v>1.978704518357234</v>
       </c>
       <c r="S17">
         <v>1</v>
@@ -1741,34 +1724,34 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
         <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="F18" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="G18" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="H18" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I18" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J18" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K18">
         <v>65</v>
@@ -1777,22 +1760,22 @@
         <v>85.79</v>
       </c>
       <c r="M18" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="N18">
         <v>147.49000549316409</v>
       </c>
       <c r="O18">
-        <v>61407.513354757248</v>
+        <v>9586.8503570556659</v>
       </c>
       <c r="P18">
-        <v>9461.91</v>
+        <v>2269.2074795150761</v>
       </c>
       <c r="Q18">
         <v>23.67</v>
       </c>
       <c r="R18">
-        <v>4.5999999999999996</v>
+        <v>1.4321988089980351</v>
       </c>
       <c r="S18">
         <v>6.4053897857666016</v>
@@ -1800,31 +1783,31 @@
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G19" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="I19" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="J19" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K19">
         <v>4</v>
@@ -1833,16 +1816,16 @@
         <v>1997.65</v>
       </c>
       <c r="M19" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="N19">
         <v>2007.300903320312</v>
       </c>
       <c r="O19">
-        <v>8029.20361328125</v>
+        <v>8029.2036132812482</v>
       </c>
       <c r="R19">
-        <v>0.6</v>
+        <v>1.1994988368292261</v>
       </c>
       <c r="S19">
         <v>1</v>
@@ -1850,34 +1833,34 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
         <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E20" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="G20" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="H20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I20" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J20" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K20">
         <v>8</v>
@@ -1886,22 +1869,22 @@
         <v>197.89</v>
       </c>
       <c r="M20" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="N20">
         <v>112.43499755859381</v>
       </c>
       <c r="O20">
-        <v>5761.5198793960744</v>
+        <v>899.47998046875045</v>
       </c>
       <c r="P20">
-        <v>-4962.07</v>
+        <v>-393.34259545898459</v>
       </c>
       <c r="Q20">
         <v>-43.73</v>
       </c>
       <c r="R20">
-        <v>0.4</v>
+        <v>0.13437511891450499</v>
       </c>
       <c r="S20">
         <v>6.4053897857666016</v>
@@ -1909,34 +1892,34 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
         <v>20</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D21" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="E21" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G21" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H21" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I21" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="J21" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K21">
         <v>69</v>
@@ -1945,7 +1928,7 @@
         <v>186.1</v>
       </c>
       <c r="M21" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="N21">
         <v>180.46000671386719</v>
@@ -1954,13 +1937,13 @@
         <v>12451.74046325684</v>
       </c>
       <c r="P21">
-        <v>218.04</v>
+        <v>211.6795878753662</v>
       </c>
       <c r="Q21">
         <v>1.7</v>
       </c>
       <c r="R21">
-        <v>0.9</v>
+        <v>1.8601904898102639</v>
       </c>
       <c r="S21">
         <v>1</v>
@@ -1968,34 +1951,34 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="E22" t="s">
-        <v>107</v>
+        <v>72</v>
       </c>
       <c r="F22" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G22" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H22" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I22" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="J22" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K22">
         <v>135</v>
@@ -2004,7 +1987,7 @@
         <v>153.84</v>
       </c>
       <c r="M22" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="N22">
         <v>180.46000671386719</v>
@@ -2013,13 +1996,13 @@
         <v>24362.10090637207</v>
       </c>
       <c r="P22">
-        <v>4781.7</v>
+        <v>5608.1556286468513</v>
       </c>
       <c r="Q22">
         <v>23.02</v>
       </c>
       <c r="R22">
-        <v>1.8</v>
+        <v>3.639503132237472</v>
       </c>
       <c r="S22">
         <v>1</v>
@@ -2027,34 +2010,34 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="E23" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="F23" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H23" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="I23" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="J23" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K23">
         <v>41</v>
@@ -2063,22 +2046,22 @@
         <v>56.83</v>
       </c>
       <c r="M23" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="N23">
         <v>92.959999084472656</v>
       </c>
       <c r="O23">
-        <v>28447.609964047329</v>
+        <v>3811.3599624633789</v>
       </c>
       <c r="P23">
-        <v>7818.84</v>
+        <v>1714.730847112274</v>
       </c>
       <c r="Q23">
         <v>44.99</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>0.56938671154759857</v>
       </c>
       <c r="S23">
         <v>7.463900089263916</v>
@@ -2086,34 +2069,34 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="E24" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="F24" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H24" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="I24" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="J24" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K24">
         <v>13</v>
@@ -2122,22 +2105,22 @@
         <v>59.4</v>
       </c>
       <c r="M24" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="N24">
         <v>92.959999084472656</v>
       </c>
       <c r="O24">
-        <v>9019.9738910393971</v>
+        <v>1208.479988098145</v>
       </c>
       <c r="P24">
-        <v>2229.9699999999998</v>
+        <v>467.92345139160147</v>
       </c>
       <c r="Q24">
         <v>38.72</v>
       </c>
       <c r="R24">
-        <v>0.7</v>
+        <v>0.18053725000289711</v>
       </c>
       <c r="S24">
         <v>7.463900089263916</v>
@@ -2145,34 +2128,34 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B25" t="s">
         <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D25" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="E25" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="F25" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H25" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="I25" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="J25" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K25">
         <v>90</v>
@@ -2181,22 +2164,22 @@
         <v>65.930000000000007</v>
       </c>
       <c r="M25" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="N25">
         <v>92.959999084472656</v>
       </c>
       <c r="O25">
-        <v>62445.973091811211</v>
+        <v>8366.3999176025391</v>
       </c>
       <c r="P25">
-        <v>11055.13</v>
+        <v>2089.9266994171139</v>
       </c>
       <c r="Q25">
         <v>24.98</v>
       </c>
       <c r="R25">
-        <v>4.5999999999999996</v>
+        <v>1.2498732692508261</v>
       </c>
       <c r="S25">
         <v>7.463900089263916</v>
@@ -2204,34 +2187,34 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B26" t="s">
         <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" t="s">
+        <v>83</v>
+      </c>
+      <c r="F26" t="s">
         <v>44</v>
       </c>
-      <c r="E26" t="s">
-        <v>102</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
-      </c>
       <c r="G26" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H26" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="I26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J26" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K26">
         <v>91</v>
@@ -2240,22 +2223,22 @@
         <v>55.55</v>
       </c>
       <c r="M26" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="N26">
         <v>57.658000946044922</v>
       </c>
       <c r="O26">
-        <v>39162.17381512469</v>
+        <v>5246.8780860900879</v>
       </c>
       <c r="P26">
-        <v>-985.45</v>
+        <v>-136.94351804695131</v>
       </c>
       <c r="Q26">
         <v>-2.61</v>
       </c>
       <c r="R26">
-        <v>2.9</v>
+        <v>0.78384164412513102</v>
       </c>
       <c r="S26">
         <v>7.463900089263916</v>
@@ -2263,34 +2246,34 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s">
         <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" t="s">
         <v>44</v>
       </c>
-      <c r="E27" t="s">
-        <v>102</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
-      </c>
       <c r="G27" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H27" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="I27" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J27" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K27">
         <v>53</v>
@@ -2299,22 +2282,22 @@
         <v>52.62</v>
       </c>
       <c r="M27" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="N27">
         <v>57.658000946044922</v>
       </c>
       <c r="O27">
-        <v>22808.738595622079</v>
+        <v>3055.8740501403809</v>
       </c>
       <c r="P27">
-        <v>583.42999999999995</v>
+        <v>85.564473403930663</v>
       </c>
       <c r="Q27">
         <v>2.8</v>
       </c>
       <c r="R27">
-        <v>1.7</v>
+        <v>0.45652315536958188</v>
       </c>
       <c r="S27">
         <v>7.463900089263916</v>
@@ -2322,34 +2305,34 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B28" t="s">
         <v>20</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D28" t="s">
+        <v>87</v>
+      </c>
+      <c r="E28" t="s">
+        <v>88</v>
+      </c>
+      <c r="F28" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" t="s">
         <v>45</v>
       </c>
-      <c r="E28" t="s">
-        <v>106</v>
-      </c>
-      <c r="F28" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28" t="s">
-        <v>57</v>
-      </c>
       <c r="H28" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="I28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J28" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K28">
         <v>61</v>
@@ -2358,22 +2341,22 @@
         <v>46.82</v>
       </c>
       <c r="M28" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="N28">
         <v>53.650001525878913</v>
       </c>
       <c r="O28">
-        <v>24426.733321859021</v>
+        <v>3272.6500930786142</v>
       </c>
       <c r="P28">
-        <v>2848.4</v>
+        <v>437.55331744461068</v>
       </c>
       <c r="Q28">
         <v>13.37</v>
       </c>
       <c r="R28">
-        <v>1.8</v>
+        <v>0.48890776334324743</v>
       </c>
       <c r="S28">
         <v>7.463900089263916</v>
@@ -2381,34 +2364,34 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F29" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G29" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H29" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="I29" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J29" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K29">
         <v>4</v>
@@ -2417,22 +2400,22 @@
         <v>430.98</v>
       </c>
       <c r="M29" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="N29">
         <v>583.15997314453125</v>
       </c>
       <c r="O29">
-        <v>17410.591102434439</v>
+        <v>2332.639892578125</v>
       </c>
       <c r="P29">
-        <v>5150.26</v>
+        <v>934.455540966797</v>
       </c>
       <c r="Q29">
         <v>40.06</v>
       </c>
       <c r="R29">
-        <v>1.3</v>
+        <v>0.34847775354216848</v>
       </c>
       <c r="S29">
         <v>7.463900089263916</v>
@@ -2440,34 +2423,34 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B30" t="s">
         <v>20</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="E30" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G30" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H30" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="I30" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J30" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K30">
         <v>21</v>
@@ -2476,22 +2459,22 @@
         <v>371.55</v>
       </c>
       <c r="M30" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="N30">
         <v>583.15997314453125</v>
       </c>
       <c r="O30">
-        <v>91405.603287780803</v>
+        <v>12246.35943603516</v>
       </c>
       <c r="P30">
-        <v>36346.800000000003</v>
+        <v>7649.0761037475604</v>
       </c>
       <c r="Q30">
         <v>62.46</v>
       </c>
       <c r="R30">
-        <v>6.8</v>
+        <v>1.829508206096385</v>
       </c>
       <c r="S30">
         <v>7.463900089263916</v>
@@ -2499,34 +2482,34 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="E31" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F31" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G31" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H31" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="I31" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J31" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K31">
         <v>11</v>
@@ -2535,22 +2518,22 @@
         <v>389.52</v>
       </c>
       <c r="M31" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="N31">
         <v>583.15997314453125</v>
       </c>
       <c r="O31">
-        <v>47879.125531694714</v>
+        <v>6414.7597045898438</v>
       </c>
       <c r="P31">
-        <v>17564.560000000001</v>
+        <v>3526.1934096130371</v>
       </c>
       <c r="Q31">
         <v>54.97</v>
       </c>
       <c r="R31">
-        <v>3.6</v>
+        <v>0.95831382224096351</v>
       </c>
       <c r="S31">
         <v>7.463900089263916</v>
@@ -2558,34 +2541,34 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B32" t="s">
         <v>20</v>
       </c>
       <c r="C32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="E32" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F32" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G32" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H32" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="I32" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J32" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K32">
         <v>7</v>
@@ -2594,22 +2577,22 @@
         <v>395.99</v>
       </c>
       <c r="M32" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="N32">
         <v>583.15997314453125</v>
       </c>
       <c r="O32">
-        <v>30468.534429260271</v>
+        <v>4082.1198120117192</v>
       </c>
       <c r="P32">
-        <v>10839.88</v>
+        <v>2140.2554174377442</v>
       </c>
       <c r="Q32">
         <v>52.43</v>
       </c>
       <c r="R32">
-        <v>2.2999999999999998</v>
+        <v>0.60983606869879492</v>
       </c>
       <c r="S32">
         <v>7.463900089263916</v>
@@ -2617,34 +2600,34 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="E33" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F33" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G33" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H33" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="I33" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J33" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K33">
         <v>18</v>
@@ -2653,22 +2636,22 @@
         <v>412.43</v>
       </c>
       <c r="M33" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="N33">
         <v>583.15997314453125</v>
       </c>
       <c r="O33">
-        <v>78347.659960954974</v>
+        <v>10496.879516601561</v>
       </c>
       <c r="P33">
-        <v>25666.44</v>
+        <v>4866.3533438964841</v>
       </c>
       <c r="Q33">
         <v>46.36</v>
       </c>
       <c r="R33">
-        <v>5.8</v>
+        <v>1.568149890939758</v>
       </c>
       <c r="S33">
         <v>7.463900089263916</v>
@@ -2676,34 +2659,34 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="E34" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F34" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="G34" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H34" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I34" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J34" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K34">
         <v>514</v>
@@ -2712,22 +2695,22 @@
         <v>6.15</v>
       </c>
       <c r="M34" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="N34">
         <v>9.5775003433227539</v>
       </c>
       <c r="O34">
-        <v>31532.67815635998</v>
+        <v>4922.8351764678964</v>
       </c>
       <c r="P34">
-        <v>10941.46</v>
+        <v>2377.2371067163472</v>
       </c>
       <c r="Q34">
         <v>48.29</v>
       </c>
       <c r="R34">
-        <v>2.2999999999999998</v>
+        <v>0.73543222372736705</v>
       </c>
       <c r="S34">
         <v>6.4053897857666016</v>
@@ -2735,34 +2718,34 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="D35" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="E35" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="F35" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G35" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H35" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="I35" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="J35" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K35">
         <v>17</v>
@@ -2771,22 +2754,22 @@
         <v>68.36</v>
       </c>
       <c r="M35" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="N35">
         <v>85.889999389648438</v>
       </c>
       <c r="O35">
-        <v>10898.264359891669</v>
+        <v>1460.129989624023</v>
       </c>
       <c r="P35">
-        <v>1085.3</v>
+        <v>182.80827470092771</v>
       </c>
       <c r="Q35">
         <v>12.52</v>
       </c>
       <c r="R35">
-        <v>0.8</v>
+        <v>0.21813174861781109</v>
       </c>
       <c r="S35">
         <v>7.463900089263916</v>
@@ -2794,34 +2777,34 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="D36" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="E36" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="F36" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G36" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H36" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="I36" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="J36" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K36">
         <v>103</v>
@@ -2830,22 +2813,22 @@
         <v>72.77</v>
       </c>
       <c r="M36" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="N36">
         <v>85.889999389648438</v>
       </c>
       <c r="O36">
-        <v>66030.660533461283</v>
+        <v>8846.6699371337891</v>
       </c>
       <c r="P36">
-        <v>2104.67</v>
+        <v>504.26018641662603</v>
       </c>
       <c r="Q36">
         <v>5.7</v>
       </c>
       <c r="R36">
-        <v>4.9000000000000004</v>
+        <v>1.3216217710373259</v>
       </c>
       <c r="S36">
         <v>7.463900089263916</v>
@@ -2853,34 +2836,34 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="B37" t="s">
         <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D37" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="E37" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="F37" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G37" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H37" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="I37" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="J37" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K37">
         <v>129</v>
@@ -2889,22 +2872,22 @@
         <v>69.91</v>
       </c>
       <c r="M37" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="N37">
         <v>85.889999389648438</v>
       </c>
       <c r="O37">
-        <v>82698.594260354439</v>
+        <v>11079.80992126465</v>
       </c>
       <c r="P37">
-        <v>6744.28</v>
+        <v>1111.304935102844</v>
       </c>
       <c r="Q37">
         <v>10.029999999999999</v>
       </c>
       <c r="R37">
-        <v>6.2</v>
+        <v>1.6552350336292729</v>
       </c>
       <c r="S37">
         <v>7.463900089263916</v>
@@ -2912,34 +2895,34 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C38" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="D38" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="E38" t="s">
-        <v>100</v>
+        <v>43</v>
       </c>
       <c r="F38" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G38" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H38" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="I38" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="J38" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K38">
         <v>15</v>
@@ -2948,22 +2931,22 @@
         <v>76.61</v>
       </c>
       <c r="M38" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="N38">
         <v>85.889999389648438</v>
       </c>
       <c r="O38">
-        <v>9616.11561166912</v>
+        <v>1288.349990844727</v>
       </c>
       <c r="P38">
-        <v>32.369999999999997</v>
+        <v>5.1533999633789058</v>
       </c>
       <c r="Q38">
         <v>0.4</v>
       </c>
       <c r="R38">
-        <v>0.7</v>
+        <v>0.19246918995689219</v>
       </c>
       <c r="S38">
         <v>7.463900089263916</v>
@@ -2971,34 +2954,34 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C39" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="D39" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="E39" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F39" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="G39" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H39" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="I39" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="J39" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K39">
         <v>190</v>
@@ -3007,22 +2990,22 @@
         <v>16.670000000000002</v>
       </c>
       <c r="M39" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="N39">
         <v>33.220001220703118</v>
       </c>
       <c r="O39">
-        <v>47110.646314545163</v>
+        <v>6311.8002319335928</v>
       </c>
       <c r="P39">
-        <v>23858.51</v>
+        <v>6633.7020437622059</v>
       </c>
       <c r="Q39">
         <v>105.1</v>
       </c>
       <c r="R39">
-        <v>3.5</v>
+        <v>0.94293250005261597</v>
       </c>
       <c r="S39">
         <v>7.463900089263916</v>
@@ -3030,34 +3013,34 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="E40" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F40" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="G40" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H40" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="I40" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="J40" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="K40">
         <v>121</v>
@@ -3066,28 +3049,29 @@
         <v>16.36</v>
       </c>
       <c r="M40" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="N40">
         <v>33.220001220703118</v>
       </c>
       <c r="O40">
-        <v>30002.043179262972</v>
+        <v>4019.6201477050772</v>
       </c>
       <c r="P40">
-        <v>16090.32</v>
+        <v>4380.9839989837637</v>
       </c>
       <c r="Q40">
         <v>108.99</v>
       </c>
       <c r="R40">
-        <v>2.2000000000000002</v>
+        <v>0.60049911845456061</v>
       </c>
       <c r="S40">
         <v>7.463900089263916</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>